--- a/Workflows/Testing/Hydraulic_Lift_Res.xlsx
+++ b/Workflows/Testing/Hydraulic_Lift_Res.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\simscape\demo\allsimscape\hydraulic-lift\Workflows\Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892ABC98-CB51-468E-8ED3-4F07189F8E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CACC435-A98E-4B06-A194-48FB3D7319DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="14" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="1665" windowWidth="26370" windowHeight="10005" firstSheet="14" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2015b" sheetId="4" r:id="rId1"/>
@@ -34,6 +34,7 @@
     <sheet name="2024b (IL1)" sheetId="25" r:id="rId19"/>
     <sheet name="2024b" sheetId="26" r:id="rId20"/>
     <sheet name="2025a" sheetId="27" r:id="rId21"/>
+    <sheet name="2026a" sheetId="28" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8609" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9135" uniqueCount="40">
   <si>
     <t>Run</t>
   </si>
@@ -171,6 +172,9 @@
   </si>
   <si>
     <t>19-Dec-2025 12:31:07</t>
+  </si>
+  <si>
+    <t>22-Apr-2026 12:10:56</t>
   </si>
 </sst>
 </file>
@@ -33617,6 +33621,2686 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4794A8A2-81F3-49D7-B474-26CED99F68CF}">
+  <dimension ref="A1:M66"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1" s="34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3">
+        <v>2264</v>
+      </c>
+      <c r="I3">
+        <v>0.31921670000000002</v>
+      </c>
+      <c r="J3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3">
+        <v>10001</v>
+      </c>
+      <c r="L3">
+        <v>0.51763630000000005</v>
+      </c>
+      <c r="M3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4">
+        <v>4544</v>
+      </c>
+      <c r="I4">
+        <v>1.4353349</v>
+      </c>
+      <c r="J4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4">
+        <v>10001</v>
+      </c>
+      <c r="L4">
+        <v>1.8330065</v>
+      </c>
+      <c r="M4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>2310</v>
+      </c>
+      <c r="I5">
+        <v>0.25287150000000003</v>
+      </c>
+      <c r="J5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5">
+        <v>10001</v>
+      </c>
+      <c r="L5">
+        <v>0.55182719999999996</v>
+      </c>
+      <c r="M5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>8566</v>
+      </c>
+      <c r="I6">
+        <v>2.8643008000000001</v>
+      </c>
+      <c r="J6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6">
+        <v>10001</v>
+      </c>
+      <c r="L6">
+        <v>1.7843141</v>
+      </c>
+      <c r="M6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7">
+        <v>2818</v>
+      </c>
+      <c r="I7">
+        <v>0.1614729</v>
+      </c>
+      <c r="J7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7">
+        <v>10001</v>
+      </c>
+      <c r="L7">
+        <v>0.51045510000000005</v>
+      </c>
+      <c r="M7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8">
+        <v>6037</v>
+      </c>
+      <c r="I8">
+        <v>1.4507645</v>
+      </c>
+      <c r="J8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8">
+        <v>10001</v>
+      </c>
+      <c r="L8">
+        <v>1.7394719000000001</v>
+      </c>
+      <c r="M8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9">
+        <v>2697</v>
+      </c>
+      <c r="I9">
+        <v>0.13226769999999999</v>
+      </c>
+      <c r="J9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9">
+        <v>10001</v>
+      </c>
+      <c r="L9">
+        <v>0.54766579999999998</v>
+      </c>
+      <c r="M9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10">
+        <v>7272</v>
+      </c>
+      <c r="I10">
+        <v>2.3775886000000002</v>
+      </c>
+      <c r="J10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10">
+        <v>10001</v>
+      </c>
+      <c r="L10">
+        <v>1.6756443999999999</v>
+      </c>
+      <c r="M10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11">
+        <v>2272</v>
+      </c>
+      <c r="I11">
+        <v>0.18567130000000001</v>
+      </c>
+      <c r="J11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11">
+        <v>10001</v>
+      </c>
+      <c r="L11">
+        <v>0.53646510000000003</v>
+      </c>
+      <c r="M11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12">
+        <v>4547</v>
+      </c>
+      <c r="I12">
+        <v>1.1265864000000001</v>
+      </c>
+      <c r="J12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12">
+        <v>10001</v>
+      </c>
+      <c r="L12">
+        <v>1.7562517</v>
+      </c>
+      <c r="M12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13">
+        <v>2311</v>
+      </c>
+      <c r="I13">
+        <v>0.1166348</v>
+      </c>
+      <c r="J13" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13">
+        <v>10001</v>
+      </c>
+      <c r="L13">
+        <v>0.51749699999999998</v>
+      </c>
+      <c r="M13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14">
+        <v>8460</v>
+      </c>
+      <c r="I14">
+        <v>2.9324751</v>
+      </c>
+      <c r="J14" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14">
+        <v>10001</v>
+      </c>
+      <c r="L14">
+        <v>1.6747904</v>
+      </c>
+      <c r="M14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15">
+        <v>2787</v>
+      </c>
+      <c r="I15">
+        <v>0.15762760000000001</v>
+      </c>
+      <c r="J15" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15">
+        <v>10001</v>
+      </c>
+      <c r="L15">
+        <v>0.52478659999999999</v>
+      </c>
+      <c r="M15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16">
+        <v>6039</v>
+      </c>
+      <c r="I16">
+        <v>1.4169917999999999</v>
+      </c>
+      <c r="J16" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16">
+        <v>10001</v>
+      </c>
+      <c r="L16">
+        <v>1.9330909999999999</v>
+      </c>
+      <c r="M16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17">
+        <v>2700</v>
+      </c>
+      <c r="I17">
+        <v>0.1574073</v>
+      </c>
+      <c r="J17" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17">
+        <v>10001</v>
+      </c>
+      <c r="L17">
+        <v>0.55649219999999999</v>
+      </c>
+      <c r="M17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18">
+        <v>7263</v>
+      </c>
+      <c r="I18">
+        <v>2.2335501999999998</v>
+      </c>
+      <c r="J18" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18">
+        <v>10001</v>
+      </c>
+      <c r="L18">
+        <v>1.9299795</v>
+      </c>
+      <c r="M18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19">
+        <v>2046</v>
+      </c>
+      <c r="I19">
+        <v>0.111919</v>
+      </c>
+      <c r="J19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K19">
+        <v>10001</v>
+      </c>
+      <c r="L19">
+        <v>0.53505329999999995</v>
+      </c>
+      <c r="M19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20">
+        <v>1663</v>
+      </c>
+      <c r="I20">
+        <v>0.54714119999999999</v>
+      </c>
+      <c r="J20" t="s">
+        <v>35</v>
+      </c>
+      <c r="K20">
+        <v>10001</v>
+      </c>
+      <c r="L20">
+        <v>1.7704101999999999</v>
+      </c>
+      <c r="M20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21">
+        <v>1997</v>
+      </c>
+      <c r="I21">
+        <v>0.14545810000000001</v>
+      </c>
+      <c r="J21" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21">
+        <v>10001</v>
+      </c>
+      <c r="L21">
+        <v>0.55821189999999998</v>
+      </c>
+      <c r="M21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22">
+        <v>1750</v>
+      </c>
+      <c r="I22">
+        <v>0.67644850000000001</v>
+      </c>
+      <c r="J22" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22">
+        <v>10001</v>
+      </c>
+      <c r="L22">
+        <v>1.748329</v>
+      </c>
+      <c r="M22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23">
+        <v>2477</v>
+      </c>
+      <c r="I23">
+        <v>0.1430206</v>
+      </c>
+      <c r="J23" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23">
+        <v>10001</v>
+      </c>
+      <c r="L23">
+        <v>0.64368219999999998</v>
+      </c>
+      <c r="M23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24">
+        <v>2459</v>
+      </c>
+      <c r="I24">
+        <v>0.90164279999999997</v>
+      </c>
+      <c r="J24" t="s">
+        <v>35</v>
+      </c>
+      <c r="K24">
+        <v>10001</v>
+      </c>
+      <c r="L24">
+        <v>1.6428862</v>
+      </c>
+      <c r="M24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" t="s">
+        <v>10</v>
+      </c>
+      <c r="H25">
+        <v>2362</v>
+      </c>
+      <c r="I25">
+        <v>0.13028200000000001</v>
+      </c>
+      <c r="J25" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25">
+        <v>10001</v>
+      </c>
+      <c r="L25">
+        <v>0.56850230000000002</v>
+      </c>
+      <c r="M25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26">
+        <v>2467</v>
+      </c>
+      <c r="I26">
+        <v>0.8574176</v>
+      </c>
+      <c r="J26" t="s">
+        <v>35</v>
+      </c>
+      <c r="K26">
+        <v>10001</v>
+      </c>
+      <c r="L26">
+        <v>1.9175399</v>
+      </c>
+      <c r="M26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27">
+        <v>2011</v>
+      </c>
+      <c r="I27">
+        <v>0.1154269</v>
+      </c>
+      <c r="J27" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27">
+        <v>10001</v>
+      </c>
+      <c r="L27">
+        <v>0.54613999999999996</v>
+      </c>
+      <c r="M27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28">
+        <v>1684</v>
+      </c>
+      <c r="I28">
+        <v>0.73066039999999999</v>
+      </c>
+      <c r="J28" t="s">
+        <v>35</v>
+      </c>
+      <c r="K28">
+        <v>10001</v>
+      </c>
+      <c r="L28">
+        <v>1.6518558999999999</v>
+      </c>
+      <c r="M28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" t="s">
+        <v>10</v>
+      </c>
+      <c r="H29">
+        <v>1899</v>
+      </c>
+      <c r="I29">
+        <v>0.1129409</v>
+      </c>
+      <c r="J29" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29">
+        <v>10001</v>
+      </c>
+      <c r="L29">
+        <v>0.59836180000000005</v>
+      </c>
+      <c r="M29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30">
+        <v>1842</v>
+      </c>
+      <c r="I30">
+        <v>0.76416459999999997</v>
+      </c>
+      <c r="J30" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30">
+        <v>10001</v>
+      </c>
+      <c r="L30">
+        <v>1.7318959</v>
+      </c>
+      <c r="M30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31">
+        <v>2407</v>
+      </c>
+      <c r="I31">
+        <v>0.1368771</v>
+      </c>
+      <c r="J31" t="s">
+        <v>35</v>
+      </c>
+      <c r="K31">
+        <v>10001</v>
+      </c>
+      <c r="L31">
+        <v>0.54889489999999996</v>
+      </c>
+      <c r="M31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32">
+        <v>2238</v>
+      </c>
+      <c r="I32">
+        <v>0.9576365</v>
+      </c>
+      <c r="J32" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32">
+        <v>10001</v>
+      </c>
+      <c r="L32">
+        <v>1.7572745000000001</v>
+      </c>
+      <c r="M32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33">
+        <v>2288</v>
+      </c>
+      <c r="I33">
+        <v>0.1455496</v>
+      </c>
+      <c r="J33" t="s">
+        <v>35</v>
+      </c>
+      <c r="K33">
+        <v>10001</v>
+      </c>
+      <c r="L33">
+        <v>0.5779183</v>
+      </c>
+      <c r="M33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34">
+        <v>2262</v>
+      </c>
+      <c r="I34">
+        <v>0.72226060000000003</v>
+      </c>
+      <c r="J34" t="s">
+        <v>35</v>
+      </c>
+      <c r="K34">
+        <v>10001</v>
+      </c>
+      <c r="L34">
+        <v>1.8795630000000001</v>
+      </c>
+      <c r="M34" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>9</v>
+      </c>
+      <c r="G35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35">
+        <v>9043</v>
+      </c>
+      <c r="I35">
+        <v>0.28728809999999999</v>
+      </c>
+      <c r="J35" t="s">
+        <v>35</v>
+      </c>
+      <c r="K35">
+        <v>10001</v>
+      </c>
+      <c r="L35">
+        <v>0.51725920000000003</v>
+      </c>
+      <c r="M35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>9</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36">
+        <v>10930</v>
+      </c>
+      <c r="I36">
+        <v>2.5059415</v>
+      </c>
+      <c r="J36" t="s">
+        <v>35</v>
+      </c>
+      <c r="K36">
+        <v>10001</v>
+      </c>
+      <c r="L36">
+        <v>1.6121416</v>
+      </c>
+      <c r="M36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" t="s">
+        <v>10</v>
+      </c>
+      <c r="H37">
+        <v>8941</v>
+      </c>
+      <c r="I37">
+        <v>0.29156310000000002</v>
+      </c>
+      <c r="J37" t="s">
+        <v>35</v>
+      </c>
+      <c r="K37">
+        <v>10001</v>
+      </c>
+      <c r="L37">
+        <v>0.54053450000000003</v>
+      </c>
+      <c r="M37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38">
+        <v>13003</v>
+      </c>
+      <c r="I38">
+        <v>4.0904604999999998</v>
+      </c>
+      <c r="J38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K38">
+        <v>10001</v>
+      </c>
+      <c r="L38">
+        <v>1.6679667</v>
+      </c>
+      <c r="M38" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39">
+        <v>10138</v>
+      </c>
+      <c r="I39">
+        <v>0.47849710000000001</v>
+      </c>
+      <c r="J39" t="s">
+        <v>35</v>
+      </c>
+      <c r="K39">
+        <v>10001</v>
+      </c>
+      <c r="L39">
+        <v>0.54410840000000005</v>
+      </c>
+      <c r="M39" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>15</v>
+      </c>
+      <c r="C40" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" t="s">
+        <v>9</v>
+      </c>
+      <c r="G40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40">
+        <v>15706</v>
+      </c>
+      <c r="I40">
+        <v>3.0635376000000001</v>
+      </c>
+      <c r="J40" t="s">
+        <v>35</v>
+      </c>
+      <c r="K40">
+        <v>10001</v>
+      </c>
+      <c r="L40">
+        <v>1.7202732999999999</v>
+      </c>
+      <c r="M40" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H41">
+        <v>10144</v>
+      </c>
+      <c r="I41">
+        <v>0.32369550000000002</v>
+      </c>
+      <c r="J41" t="s">
+        <v>35</v>
+      </c>
+      <c r="K41">
+        <v>10001</v>
+      </c>
+      <c r="L41">
+        <v>0.55292540000000001</v>
+      </c>
+      <c r="M41" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42">
+        <v>14742</v>
+      </c>
+      <c r="I42">
+        <v>4.4355076999999996</v>
+      </c>
+      <c r="J42" t="s">
+        <v>35</v>
+      </c>
+      <c r="K42">
+        <v>10001</v>
+      </c>
+      <c r="L42">
+        <v>1.6807325</v>
+      </c>
+      <c r="M42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" t="s">
+        <v>9</v>
+      </c>
+      <c r="G43" t="s">
+        <v>10</v>
+      </c>
+      <c r="H43">
+        <v>9049</v>
+      </c>
+      <c r="I43">
+        <v>0.29917769999999999</v>
+      </c>
+      <c r="J43" t="s">
+        <v>35</v>
+      </c>
+      <c r="K43">
+        <v>10001</v>
+      </c>
+      <c r="L43">
+        <v>0.54331280000000004</v>
+      </c>
+      <c r="M43" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" t="s">
+        <v>9</v>
+      </c>
+      <c r="G44" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44">
+        <v>10925</v>
+      </c>
+      <c r="I44">
+        <v>2.5889650999999998</v>
+      </c>
+      <c r="J44" t="s">
+        <v>35</v>
+      </c>
+      <c r="K44">
+        <v>10001</v>
+      </c>
+      <c r="L44">
+        <v>1.8733165000000001</v>
+      </c>
+      <c r="M44" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45">
+        <v>8959</v>
+      </c>
+      <c r="I45">
+        <v>0.27519719999999998</v>
+      </c>
+      <c r="J45" t="s">
+        <v>35</v>
+      </c>
+      <c r="K45">
+        <v>10001</v>
+      </c>
+      <c r="L45">
+        <v>0.53534510000000002</v>
+      </c>
+      <c r="M45" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46">
+        <v>12959</v>
+      </c>
+      <c r="I46">
+        <v>4.2505275999999999</v>
+      </c>
+      <c r="J46" t="s">
+        <v>35</v>
+      </c>
+      <c r="K46">
+        <v>10001</v>
+      </c>
+      <c r="L46">
+        <v>1.8777101</v>
+      </c>
+      <c r="M46" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" t="s">
+        <v>9</v>
+      </c>
+      <c r="G47" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47">
+        <v>10116</v>
+      </c>
+      <c r="I47">
+        <v>0.542103</v>
+      </c>
+      <c r="J47" t="s">
+        <v>35</v>
+      </c>
+      <c r="K47">
+        <v>10001</v>
+      </c>
+      <c r="L47">
+        <v>0.54560359999999997</v>
+      </c>
+      <c r="M47" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" t="s">
+        <v>9</v>
+      </c>
+      <c r="G48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48">
+        <v>15671</v>
+      </c>
+      <c r="I48">
+        <v>3.1491533999999999</v>
+      </c>
+      <c r="J48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K48">
+        <v>10001</v>
+      </c>
+      <c r="L48">
+        <v>1.6934209</v>
+      </c>
+      <c r="M48" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" t="s">
+        <v>12</v>
+      </c>
+      <c r="G49" t="s">
+        <v>10</v>
+      </c>
+      <c r="H49">
+        <v>10083</v>
+      </c>
+      <c r="I49">
+        <v>0.33158349999999998</v>
+      </c>
+      <c r="J49" t="s">
+        <v>35</v>
+      </c>
+      <c r="K49">
+        <v>10001</v>
+      </c>
+      <c r="L49">
+        <v>0.553257</v>
+      </c>
+      <c r="M49" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50">
+        <v>14749</v>
+      </c>
+      <c r="I50">
+        <v>4.4995748999999998</v>
+      </c>
+      <c r="J50" t="s">
+        <v>35</v>
+      </c>
+      <c r="K50">
+        <v>10001</v>
+      </c>
+      <c r="L50">
+        <v>1.7702690000000001</v>
+      </c>
+      <c r="M50" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" t="s">
+        <v>9</v>
+      </c>
+      <c r="G51" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51">
+        <v>9673</v>
+      </c>
+      <c r="I51">
+        <v>0.30788919999999997</v>
+      </c>
+      <c r="J51" t="s">
+        <v>35</v>
+      </c>
+      <c r="K51">
+        <v>10001</v>
+      </c>
+      <c r="L51">
+        <v>0.55221220000000004</v>
+      </c>
+      <c r="M51" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" t="s">
+        <v>9</v>
+      </c>
+      <c r="F52" t="s">
+        <v>9</v>
+      </c>
+      <c r="G52" t="s">
+        <v>11</v>
+      </c>
+      <c r="H52">
+        <v>10035</v>
+      </c>
+      <c r="I52">
+        <v>2.5991365000000002</v>
+      </c>
+      <c r="J52" t="s">
+        <v>35</v>
+      </c>
+      <c r="K52">
+        <v>10001</v>
+      </c>
+      <c r="L52">
+        <v>1.6091131000000001</v>
+      </c>
+      <c r="M52" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53" t="s">
+        <v>10</v>
+      </c>
+      <c r="H53">
+        <v>9515</v>
+      </c>
+      <c r="I53">
+        <v>0.33995249999999999</v>
+      </c>
+      <c r="J53" t="s">
+        <v>35</v>
+      </c>
+      <c r="K53">
+        <v>10001</v>
+      </c>
+      <c r="L53">
+        <v>0.63614349999999997</v>
+      </c>
+      <c r="M53" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" t="s">
+        <v>11</v>
+      </c>
+      <c r="H54">
+        <v>8916</v>
+      </c>
+      <c r="I54">
+        <v>2.3135826000000002</v>
+      </c>
+      <c r="J54" t="s">
+        <v>35</v>
+      </c>
+      <c r="K54">
+        <v>10001</v>
+      </c>
+      <c r="L54">
+        <v>1.7190296</v>
+      </c>
+      <c r="M54" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" t="s">
+        <v>9</v>
+      </c>
+      <c r="G55" t="s">
+        <v>10</v>
+      </c>
+      <c r="H55">
+        <v>10256</v>
+      </c>
+      <c r="I55">
+        <v>0.31038680000000002</v>
+      </c>
+      <c r="J55" t="s">
+        <v>35</v>
+      </c>
+      <c r="K55">
+        <v>10001</v>
+      </c>
+      <c r="L55">
+        <v>0.50191989999999997</v>
+      </c>
+      <c r="M55" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>15</v>
+      </c>
+      <c r="C56" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" t="s">
+        <v>9</v>
+      </c>
+      <c r="G56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56">
+        <v>13488</v>
+      </c>
+      <c r="I56">
+        <v>3.4464684000000001</v>
+      </c>
+      <c r="J56" t="s">
+        <v>35</v>
+      </c>
+      <c r="K56">
+        <v>10001</v>
+      </c>
+      <c r="L56">
+        <v>1.7138329000000001</v>
+      </c>
+      <c r="M56" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" t="s">
+        <v>12</v>
+      </c>
+      <c r="G57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H57">
+        <v>10104</v>
+      </c>
+      <c r="I57">
+        <v>0.34121679999999999</v>
+      </c>
+      <c r="J57" t="s">
+        <v>35</v>
+      </c>
+      <c r="K57">
+        <v>10001</v>
+      </c>
+      <c r="L57">
+        <v>0.52048830000000001</v>
+      </c>
+      <c r="M57" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58">
+        <v>12783</v>
+      </c>
+      <c r="I58">
+        <v>3.2376312999999999</v>
+      </c>
+      <c r="J58" t="s">
+        <v>35</v>
+      </c>
+      <c r="K58">
+        <v>10001</v>
+      </c>
+      <c r="L58">
+        <v>1.7883397999999999</v>
+      </c>
+      <c r="M58" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" t="s">
+        <v>9</v>
+      </c>
+      <c r="G59" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59">
+        <v>9496</v>
+      </c>
+      <c r="I59">
+        <v>0.53301989999999999</v>
+      </c>
+      <c r="J59" t="s">
+        <v>35</v>
+      </c>
+      <c r="K59">
+        <v>10001</v>
+      </c>
+      <c r="L59">
+        <v>0.54552849999999997</v>
+      </c>
+      <c r="M59" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" t="s">
+        <v>9</v>
+      </c>
+      <c r="G60" t="s">
+        <v>11</v>
+      </c>
+      <c r="H60">
+        <v>9978</v>
+      </c>
+      <c r="I60">
+        <v>2.6861518000000002</v>
+      </c>
+      <c r="J60" t="s">
+        <v>35</v>
+      </c>
+      <c r="K60">
+        <v>10001</v>
+      </c>
+      <c r="L60">
+        <v>1.7688390000000001</v>
+      </c>
+      <c r="M60" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" t="s">
+        <v>12</v>
+      </c>
+      <c r="G61" t="s">
+        <v>10</v>
+      </c>
+      <c r="H61">
+        <v>9428</v>
+      </c>
+      <c r="I61">
+        <v>0.3111275</v>
+      </c>
+      <c r="J61" t="s">
+        <v>35</v>
+      </c>
+      <c r="K61">
+        <v>10001</v>
+      </c>
+      <c r="L61">
+        <v>0.5258311</v>
+      </c>
+      <c r="M61" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G62" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62">
+        <v>8866</v>
+      </c>
+      <c r="I62">
+        <v>2.8986227000000002</v>
+      </c>
+      <c r="J62" t="s">
+        <v>35</v>
+      </c>
+      <c r="K62">
+        <v>10001</v>
+      </c>
+      <c r="L62">
+        <v>1.7968687999999999</v>
+      </c>
+      <c r="M62" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63" t="s">
+        <v>17</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" t="s">
+        <v>9</v>
+      </c>
+      <c r="G63" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63">
+        <v>10102</v>
+      </c>
+      <c r="I63">
+        <v>0.33068110000000001</v>
+      </c>
+      <c r="J63" t="s">
+        <v>35</v>
+      </c>
+      <c r="K63">
+        <v>10001</v>
+      </c>
+      <c r="L63">
+        <v>0.55981110000000001</v>
+      </c>
+      <c r="M63" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G64" t="s">
+        <v>11</v>
+      </c>
+      <c r="H64">
+        <v>13299</v>
+      </c>
+      <c r="I64">
+        <v>3.3163068999999998</v>
+      </c>
+      <c r="J64" t="s">
+        <v>35</v>
+      </c>
+      <c r="K64">
+        <v>10001</v>
+      </c>
+      <c r="L64">
+        <v>1.8384309999999999</v>
+      </c>
+      <c r="M64" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" t="s">
+        <v>17</v>
+      </c>
+      <c r="D65" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65" t="s">
+        <v>10</v>
+      </c>
+      <c r="H65">
+        <v>10035</v>
+      </c>
+      <c r="I65">
+        <v>0.32576260000000001</v>
+      </c>
+      <c r="J65" t="s">
+        <v>35</v>
+      </c>
+      <c r="K65">
+        <v>10001</v>
+      </c>
+      <c r="L65">
+        <v>0.52509740000000005</v>
+      </c>
+      <c r="M65" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" t="s">
+        <v>12</v>
+      </c>
+      <c r="G66" t="s">
+        <v>11</v>
+      </c>
+      <c r="H66">
+        <v>12638</v>
+      </c>
+      <c r="I66">
+        <v>3.0406692999999998</v>
+      </c>
+      <c r="J66" t="s">
+        <v>35</v>
+      </c>
+      <c r="K66">
+        <v>10001</v>
+      </c>
+      <c r="L66">
+        <v>1.840498</v>
+      </c>
+      <c r="M66" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K66"/>
